--- a/DIESEL SERFOCOL- V01.xlsx
+++ b/DIESEL SERFOCOL- V01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\STREAMLIT WEB\SERFOCOL PROGRAMACION PY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B18748DF-0169-4DC2-BA3B-7E046E6C0496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98618270-3BE3-4AFC-B22F-0EFE5D943326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DIESEL SERFOCOL" sheetId="1" r:id="rId1"/>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="40">
   <si>
     <t>Planta</t>
   </si>
@@ -3511,7 +3511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1019"/>
+  <dimension ref="A1:F1035"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.6328125" customWidth="1"/>
@@ -3549,8 +3549,8 @@
         <v>20</v>
       </c>
       <c r="B6" s="5">
-        <f>+F299</f>
-        <v>14864</v>
+        <f>+F315</f>
+        <v>15401</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -9370,44 +9370,318 @@
       </c>
     </row>
     <row r="299" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A299" s="5"/>
-      <c r="B299" s="5"/>
-      <c r="C299" s="5"/>
-      <c r="D299" s="5"/>
-      <c r="E299" s="5"/>
-      <c r="F299" s="5">
-        <f>SUBTOTAL(109,(F10:F298))</f>
-        <v>14864</v>
+      <c r="A299" s="4">
+        <v>46266</v>
+      </c>
+      <c r="B299" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C299" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D299" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E299" s="5">
+        <v>1646</v>
+      </c>
+      <c r="F299" s="13">
+        <v>50</v>
       </c>
     </row>
     <row r="300" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A300" s="5"/>
-      <c r="B300" s="5"/>
-      <c r="C300" s="5"/>
-      <c r="D300" s="5"/>
-      <c r="E300" s="5"/>
-      <c r="F300" s="5"/>
-    </row>
-    <row r="301" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="302" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="303" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="304" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="305" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="306" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="307" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="308" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="309" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="310" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="311" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="312" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="313" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="314" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="315" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="316" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="317" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="318" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="319" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="320" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+      <c r="A300" s="4">
+        <v>46270</v>
+      </c>
+      <c r="B300" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C300" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D300" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E300" s="5">
+        <v>1647</v>
+      </c>
+      <c r="F300" s="13">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A301" s="4">
+        <v>46274</v>
+      </c>
+      <c r="B301" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C301" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D301" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E301" s="5">
+        <v>1648</v>
+      </c>
+      <c r="F301" s="13">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A302" s="4">
+        <v>46279</v>
+      </c>
+      <c r="B302" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C302" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D302" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E302" s="5">
+        <v>1649</v>
+      </c>
+      <c r="F302" s="13">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A303" s="4">
+        <v>46282</v>
+      </c>
+      <c r="B303" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C303" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D303" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E303" s="5">
+        <v>1650</v>
+      </c>
+      <c r="F303" s="13">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A304" s="4">
+        <v>46291</v>
+      </c>
+      <c r="B304" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C304" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D304" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E304" s="5">
+        <v>3762</v>
+      </c>
+      <c r="F304" s="13">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A305" s="4">
+        <v>46295</v>
+      </c>
+      <c r="B305" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C305" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D305" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E305" s="5">
+        <v>3763</v>
+      </c>
+      <c r="F305" s="13">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A306" s="4">
+        <v>46300</v>
+      </c>
+      <c r="B306" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C306" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D306" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E306" s="5">
+        <v>3764</v>
+      </c>
+      <c r="F306" s="13">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A307" s="4">
+        <v>46302</v>
+      </c>
+      <c r="B307" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C307" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D307" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E307" s="5">
+        <v>3765</v>
+      </c>
+      <c r="F307" s="13">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A308" s="4">
+        <v>46305</v>
+      </c>
+      <c r="B308" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C308" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D308" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E308" s="5">
+        <v>3766</v>
+      </c>
+      <c r="F308" s="13">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A309" s="4">
+        <v>46309</v>
+      </c>
+      <c r="B309" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C309" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D309" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E309" s="5">
+        <v>3767</v>
+      </c>
+      <c r="F309" s="13">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A310" s="4"/>
+      <c r="B310" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C310" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D310" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E310" s="5"/>
+      <c r="F310" s="13"/>
+    </row>
+    <row r="311" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A311" s="4"/>
+      <c r="B311" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C311" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D311" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E311" s="5"/>
+      <c r="F311" s="13"/>
+    </row>
+    <row r="312" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A312" s="4"/>
+      <c r="B312" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C312" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D312" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E312" s="5"/>
+      <c r="F312" s="13"/>
+    </row>
+    <row r="313" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A313" s="4"/>
+      <c r="B313" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C313" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D313" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E313" s="5"/>
+      <c r="F313" s="13"/>
+    </row>
+    <row r="314" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A314" s="4"/>
+      <c r="B314" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C314" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D314" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E314" s="5"/>
+      <c r="F314" s="13"/>
+    </row>
+    <row r="315" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A315" s="5"/>
+      <c r="B315" s="5"/>
+      <c r="C315" s="5"/>
+      <c r="D315" s="5"/>
+      <c r="E315" s="5"/>
+      <c r="F315" s="5">
+        <f>SUBTOTAL(109,(F10:F314))</f>
+        <v>15401</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A316" s="5"/>
+      <c r="B316" s="5"/>
+      <c r="C316" s="5"/>
+      <c r="D316" s="5"/>
+      <c r="E316" s="5"/>
+      <c r="F316" s="5"/>
+    </row>
+    <row r="317" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="318" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="319" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="320" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="321" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="322" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="323" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -10107,6 +10381,22 @@
     <row r="1017" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="1018" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="1019" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1020" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1021" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1022" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1023" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1024" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1025" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1026" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1027" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1028" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1029" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1030" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1031" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1032" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1033" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1034" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1035" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <autoFilter ref="A9:F281" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
